--- a/dados_laranja.xlsx
+++ b/dados_laranja.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/cHALLENGE lek/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/Dados Desafio LEK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{268DFBAD-898C-4933-BE24-9CA039292CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{268DFBAD-898C-4933-BE24-9CA039292CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D85E7F2F-0F4C-4EA6-B916-658B3DC14952}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8137CB04-77A6-42B0-9E44-92C8B23DCAB6}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="182">
   <si>
     <t>Commodity</t>
   </si>
@@ -1064,13 +1064,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1553,888 +1550,922 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>978</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>980</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <v>859</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="2">
         <v>938</v>
       </c>
-      <c r="X2" s="3">
+      <c r="X2" s="2">
         <v>944</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="3">
+      <c r="AA2" s="2">
         <v>828.755</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AB2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AC2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>0</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3">
-        <v>0</v>
-      </c>
-      <c r="T3" s="3">
-        <v>0</v>
-      </c>
-      <c r="U3" s="3">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3">
-        <v>0</v>
-      </c>
-      <c r="X3" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="3" t="s">
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>962</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <v>989</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="W4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Y4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="Z4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="2">
         <v>777.02499999999998</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="2">
         <v>953.84</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AC4" s="2">
         <v>973.27599999999995</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AD4" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>15</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>15</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>18</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>20</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>23</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>28</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>31</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>34</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>34</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>35</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>40</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>44</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>45</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>35</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>35</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>38</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <v>38</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <v>40</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <v>52</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <v>63</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <v>70</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <v>73</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <v>75</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="2">
         <v>55</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AB5" s="2">
         <v>58</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AC5" s="2">
         <v>58.7</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AD5" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>151</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>240</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>56</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>101</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>18</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>15</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>166</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>172</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>128</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <v>65</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <v>440</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="2">
         <v>509</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>334</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>329</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <v>147</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <v>6</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="2">
         <v>185</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="2">
         <v>160</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="2">
         <v>312</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6" s="2">
         <v>151</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="2">
         <v>15</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="2">
         <v>9</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="2">
         <v>8.17</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AB6" s="2">
         <v>5.9</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AC6" s="2">
         <v>6</v>
       </c>
-      <c r="AD6" s="3" t="s">
+      <c r="AD6" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="P7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="Q7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="R7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="S7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="T7" s="3" t="s">
+      <c r="T7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="U7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="V7" s="3" t="s">
+      <c r="V7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="W7" s="3" t="s">
+      <c r="W7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="X7" s="3" t="s">
+      <c r="X7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="Y7" s="3" t="s">
+      <c r="Y7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Z7" s="3" t="s">
+      <c r="Z7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AA7" s="3" t="s">
+      <c r="AA7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AB7" s="3" t="s">
+      <c r="AB7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AC7" s="3" t="s">
+      <c r="AC7" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AD7" s="3" t="s">
+      <c r="AD7" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>519.70399999999995</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="Q8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="S8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="T8" s="3" t="s">
+      <c r="T8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="U8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="V8" s="3" t="s">
+      <c r="V8" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="W8" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="X8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="Y8" s="3" t="s">
+      <c r="Y8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="Z8" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AA8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AB8" s="3" t="s">
+      <c r="AB8" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AC8" s="3" t="s">
+      <c r="AC8" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AD8" s="3" t="s">
+      <c r="AD8" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="Q9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="R9" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="T9" s="3" t="s">
+      <c r="T9" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="U9" s="3" t="s">
+      <c r="U9" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="V9" s="3" t="s">
+      <c r="V9" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="W9" s="3" t="s">
+      <c r="W9" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="X9" s="3" t="s">
+      <c r="X9" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="Y9" s="3" t="s">
+      <c r="Y9" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="Z9" s="3" t="s">
+      <c r="Z9" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="AA9" s="3" t="s">
+      <c r="AA9" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="AB9" s="3" t="s">
+      <c r="AB9" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="AC9" s="3" t="s">
+      <c r="AC9" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="AD9" s="3" t="s">
+      <c r="AD9" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="O10" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="P10" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="Q10" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="R10" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="S10" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="T10" s="3" t="s">
+      <c r="T10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="U10" s="3" t="s">
+      <c r="U10" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="V10" s="3" t="s">
+      <c r="V10" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="W10" s="3" t="s">
+      <c r="W10" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="X10" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="Y10" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Z10" s="3" t="s">
+      <c r="Z10" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AA10" s="3" t="s">
+      <c r="AA10" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AB10" s="3" t="s">
+      <c r="AB10" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AC10" s="3" t="s">
+      <c r="AC10" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AD10" s="3" t="s">
+      <c r="AD10" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>732.48500000000001</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>811.71100000000001</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>624.55499999999995</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>749.94</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>525.02</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>426.613</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>485.78399999999999</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <v>695.47199999999998</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>695.59400000000005</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <v>533.697</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <v>827.35400000000004</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="2">
         <v>926.43299999999999</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="2">
         <v>803.61500000000001</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <v>764.06100000000004</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="2">
         <v>593.10900000000004</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="2">
         <v>374.04700000000003</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="2">
         <v>507.178</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="2">
         <v>476.584</v>
       </c>
-      <c r="V11" s="3">
+      <c r="V11" s="2">
         <v>775.76199999999994</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W11" s="2">
         <v>515.08399999999995</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="2">
         <v>317.73700000000002</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="2">
         <v>222.875</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z11" s="2">
         <v>189.58099999999999</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="2">
         <v>227.29300000000001</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AB11" s="2">
         <v>250.23500000000001</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="2">
         <v>249.51499999999999</v>
       </c>
-      <c r="AD11" s="3" t="s">
+      <c r="AD11" s="2" t="s">
         <v>53</v>
       </c>
     </row>
